--- a/New_ROM/Data Files/Model 15 ROM Data.xlsx
+++ b/New_ROM/Data Files/Model 15 ROM Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="4N"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="13">
   <si>
     <t>Descriptions:</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>Z (UR3)</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -155,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -236,9 +233,6 @@
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -654,45 +648,35 @@
       <c r="AC2" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="28" t="s">
-        <v>13</v>
-      </c>
+      <c r="A3" s="10"/>
       <c r="B3" s="11">
         <v>1</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="28" t="s">
-        <v>13</v>
-      </c>
+      <c r="F3" s="10"/>
       <c r="G3" s="11">
         <v>18</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="28" t="s">
-        <v>13</v>
-      </c>
+      <c r="K3" s="10"/>
       <c r="L3" s="12">
         <v>19</v>
       </c>
       <c r="M3" s="13"/>
       <c r="N3" s="13"/>
       <c r="O3" s="3"/>
-      <c r="P3" s="28" t="s">
-        <v>13</v>
-      </c>
+      <c r="P3" s="10"/>
       <c r="Q3" s="12">
         <v>20</v>
       </c>
       <c r="R3" s="13"/>
       <c r="S3" s="13"/>
       <c r="T3" s="3"/>
-      <c r="U3" s="28" t="s">
-        <v>13</v>
-      </c>
+      <c r="U3" s="10"/>
       <c r="V3" s="12">
         <v>21</v>
       </c>
